--- a/Modulo/UTI.xlsx
+++ b/Modulo/UTI.xlsx
@@ -49411,7 +49411,7 @@
       <c r="W518" t="inlineStr"/>
       <c r="X518" t="inlineStr"/>
       <c r="Y518" t="n">
-        <v>792.5150000000001</v>
+        <v>792.148</v>
       </c>
       <c r="Z518" t="n">
         <v>748.09</v>
@@ -49511,7 +49511,7 @@
       <c r="W519" t="inlineStr"/>
       <c r="X519" t="inlineStr"/>
       <c r="Y519" t="n">
-        <v>488.063</v>
+        <v>492.061</v>
       </c>
       <c r="Z519" t="n">
         <v>414.81</v>
@@ -49611,7 +49611,7 @@
       <c r="W520" t="inlineStr"/>
       <c r="X520" t="inlineStr"/>
       <c r="Y520" t="n">
-        <v>2513.554</v>
+        <v>2530.581</v>
       </c>
       <c r="Z520" t="n">
         <v>2435.45</v>
@@ -58265,10 +58265,10 @@
       <c r="W609" t="inlineStr"/>
       <c r="X609" t="inlineStr"/>
       <c r="Y609" t="n">
-        <v>65241.708</v>
+        <v>67050.25599999999</v>
       </c>
       <c r="Z609" t="n">
-        <v>54034.25</v>
+        <v>56540.5</v>
       </c>
       <c r="AA609" t="n">
         <v>1525.08472</v>
@@ -58359,10 +58359,10 @@
       <c r="W610" t="inlineStr"/>
       <c r="X610" t="inlineStr"/>
       <c r="Y610" t="n">
-        <v>1773.056</v>
+        <v>1775.949</v>
       </c>
       <c r="Z610" t="n">
-        <v>1765.31</v>
+        <v>1744.71</v>
       </c>
       <c r="AA610" t="n">
         <v>0</v>
@@ -58453,7 +58453,7 @@
       <c r="W611" t="inlineStr"/>
       <c r="X611" t="inlineStr"/>
       <c r="Y611" t="n">
-        <v>526.22</v>
+        <v>526.72</v>
       </c>
       <c r="Z611" t="n">
         <v>496.97</v>
@@ -58547,10 +58547,10 @@
       <c r="W612" t="inlineStr"/>
       <c r="X612" t="inlineStr"/>
       <c r="Y612" t="n">
-        <v>9084.194</v>
+        <v>9469.769</v>
       </c>
       <c r="Z612" t="n">
-        <v>7013.22</v>
+        <v>7541.62</v>
       </c>
       <c r="AA612" t="n">
         <v>152.135</v>
@@ -58641,10 +58641,10 @@
       <c r="W613" t="inlineStr"/>
       <c r="X613" t="inlineStr"/>
       <c r="Y613" t="n">
-        <v>2250.348</v>
+        <v>2314.428</v>
       </c>
       <c r="Z613" t="n">
-        <v>1553.11</v>
+        <v>1605.42</v>
       </c>
       <c r="AA613" t="n">
         <v>0</v>
@@ -58735,7 +58735,7 @@
       <c r="W614" t="inlineStr"/>
       <c r="X614" t="inlineStr"/>
       <c r="Y614" t="n">
-        <v>11625.936</v>
+        <v>11702.866</v>
       </c>
       <c r="Z614" t="n">
         <v>14748.17</v>
@@ -58829,10 +58829,10 @@
       <c r="W615" t="inlineStr"/>
       <c r="X615" t="inlineStr"/>
       <c r="Y615" t="n">
-        <v>31064.53</v>
+        <v>31110.51</v>
       </c>
       <c r="Z615" t="n">
-        <v>25772.83</v>
+        <v>30632.69</v>
       </c>
       <c r="AA615" t="n">
         <v>627.3</v>
@@ -58923,7 +58923,7 @@
       <c r="W616" t="inlineStr"/>
       <c r="X616" t="inlineStr"/>
       <c r="Y616" t="n">
-        <v>1441.51</v>
+        <v>1435.21</v>
       </c>
       <c r="Z616" t="n">
         <v>913.34</v>
@@ -59017,10 +59017,10 @@
       <c r="W617" t="inlineStr"/>
       <c r="X617" t="inlineStr"/>
       <c r="Y617" t="n">
-        <v>5928.320000000001</v>
+        <v>5929.26</v>
       </c>
       <c r="Z617" t="n">
-        <v>6143.84</v>
+        <v>6170.84</v>
       </c>
       <c r="AA617" t="n">
         <v>506.15</v>
@@ -59111,7 +59111,7 @@
       <c r="W618" t="inlineStr"/>
       <c r="X618" t="inlineStr"/>
       <c r="Y618" t="n">
-        <v>193.6</v>
+        <v>194.42</v>
       </c>
       <c r="Z618" t="n">
         <v>201.03</v>
@@ -59205,7 +59205,7 @@
       <c r="W619" t="inlineStr"/>
       <c r="X619" t="inlineStr"/>
       <c r="Y619" t="n">
-        <v>232.62</v>
+        <v>231.06</v>
       </c>
       <c r="Z619" t="n">
         <v>252.49</v>
@@ -59299,7 +59299,7 @@
       <c r="W620" t="inlineStr"/>
       <c r="X620" t="inlineStr"/>
       <c r="Y620" t="n">
-        <v>2478.92</v>
+        <v>2528.55</v>
       </c>
       <c r="Z620" t="n">
         <v>1126.97</v>
@@ -59393,10 +59393,10 @@
       <c r="W621" t="inlineStr"/>
       <c r="X621" t="inlineStr"/>
       <c r="Y621" t="n">
-        <v>794.996</v>
+        <v>795.652</v>
       </c>
       <c r="Z621" t="n">
-        <v>186</v>
+        <v>677.84</v>
       </c>
       <c r="AA621" t="n">
         <v>9.15</v>
@@ -59481,13 +59481,13 @@
       <c r="W622" t="inlineStr"/>
       <c r="X622" t="inlineStr"/>
       <c r="Y622" t="n">
-        <v>2809.262</v>
+        <v>2718.672</v>
       </c>
       <c r="Z622" t="n">
-        <v>0</v>
+        <v>2822.33</v>
       </c>
       <c r="AA622" t="n">
-        <v>0</v>
+        <v>472.80781</v>
       </c>
       <c r="AB622" t="inlineStr">
         <is>
@@ -61121,10 +61121,10 @@
       <c r="W642" t="inlineStr"/>
       <c r="X642" t="inlineStr"/>
       <c r="Y642" t="n">
-        <v>17719.872</v>
+        <v>17830.773</v>
       </c>
       <c r="Z642" t="n">
-        <v>18745.86</v>
+        <v>18860.33</v>
       </c>
       <c r="AA642" t="n">
         <v>4472.23196</v>
@@ -62354,15 +62354,9 @@
       <c r="V656" t="inlineStr"/>
       <c r="W656" t="inlineStr"/>
       <c r="X656" t="inlineStr"/>
-      <c r="Y656" t="n">
-        <v>693.404</v>
-      </c>
-      <c r="Z656" t="n">
-        <v>655.2</v>
-      </c>
-      <c r="AA656" t="n">
-        <v>84.64404</v>
-      </c>
+      <c r="Y656" t="inlineStr"/>
+      <c r="Z656" t="inlineStr"/>
+      <c r="AA656" t="inlineStr"/>
       <c r="AB656" t="inlineStr">
         <is>
           <t>SAMA I MODULO</t>
@@ -62443,10 +62437,10 @@
       <c r="W657" t="inlineStr"/>
       <c r="X657" t="inlineStr"/>
       <c r="Y657" t="n">
-        <v>9586.972</v>
+        <v>8925.786</v>
       </c>
       <c r="Z657" t="n">
-        <v>8816.210000000001</v>
+        <v>8816.209999999999</v>
       </c>
       <c r="AA657" t="n">
         <v>1569.0345</v>
@@ -62701,7 +62695,7 @@
       <c r="W660" t="inlineStr"/>
       <c r="X660" t="inlineStr"/>
       <c r="Y660" t="n">
-        <v>3478.25</v>
+        <v>3483.341</v>
       </c>
       <c r="Z660" t="n">
         <v>3403.02</v>
@@ -63147,7 +63141,7 @@
       <c r="W665" t="inlineStr"/>
       <c r="X665" t="inlineStr"/>
       <c r="Y665" t="n">
-        <v>300.39</v>
+        <v>299.1899999999999</v>
       </c>
       <c r="Z665" t="n">
         <v>257.44</v>
@@ -63329,7 +63323,7 @@
       <c r="W667" t="inlineStr"/>
       <c r="X667" t="inlineStr"/>
       <c r="Y667" t="n">
-        <v>172.06</v>
+        <v>171.46</v>
       </c>
       <c r="Z667" t="n">
         <v>152.04</v>
@@ -63598,9 +63592,15 @@
       <c r="V670" t="inlineStr"/>
       <c r="W670" t="inlineStr"/>
       <c r="X670" t="inlineStr"/>
-      <c r="Y670" t="inlineStr"/>
-      <c r="Z670" t="inlineStr"/>
-      <c r="AA670" t="inlineStr"/>
+      <c r="Y670" t="n">
+        <v>644.982</v>
+      </c>
+      <c r="Z670" t="n">
+        <v>310.5</v>
+      </c>
+      <c r="AA670" t="n">
+        <v>49.82749</v>
+      </c>
       <c r="AB670" t="inlineStr">
         <is>
           <t>SAMA I MODULO</t>
@@ -63857,10 +63857,10 @@
       <c r="W673" t="inlineStr"/>
       <c r="X673" t="inlineStr"/>
       <c r="Y673" t="n">
-        <v>212.02</v>
+        <v>248.066</v>
       </c>
       <c r="Z673" t="n">
-        <v>193.01</v>
+        <v>219.48</v>
       </c>
       <c r="AA673" t="n">
         <v>0</v>
@@ -63945,7 +63945,7 @@
       <c r="W674" t="inlineStr"/>
       <c r="X674" t="inlineStr"/>
       <c r="Y674" t="n">
-        <v>12821.899</v>
+        <v>12576.038</v>
       </c>
       <c r="Z674" t="n">
         <v>6881.32</v>
@@ -64039,7 +64039,7 @@
       <c r="W675" t="inlineStr"/>
       <c r="X675" t="inlineStr"/>
       <c r="Y675" t="n">
-        <v>7975.519</v>
+        <v>8073.343</v>
       </c>
       <c r="Z675" t="n">
         <v>7546.02</v>
@@ -64133,7 +64133,7 @@
       <c r="W676" t="inlineStr"/>
       <c r="X676" t="inlineStr"/>
       <c r="Y676" t="n">
-        <v>8336.442000000001</v>
+        <v>8400.416999999999</v>
       </c>
       <c r="Z676" t="n">
         <v>8082.679999999999</v>
@@ -64227,7 +64227,7 @@
       <c r="W677" t="inlineStr"/>
       <c r="X677" t="inlineStr"/>
       <c r="Y677" t="n">
-        <v>293.749</v>
+        <v>293.559</v>
       </c>
       <c r="Z677" t="n">
         <v>256.11</v>
@@ -64315,10 +64315,10 @@
       <c r="W678" t="inlineStr"/>
       <c r="X678" t="inlineStr"/>
       <c r="Y678" t="n">
-        <v>2961.166</v>
+        <v>3152.263</v>
       </c>
       <c r="Z678" t="n">
-        <v>2872.14</v>
+        <v>3047.08</v>
       </c>
       <c r="AA678" t="n">
         <v>686.03133</v>
@@ -64403,7 +64403,7 @@
       <c r="W679" t="inlineStr"/>
       <c r="X679" t="inlineStr"/>
       <c r="Y679" t="n">
-        <v>7610.924</v>
+        <v>7618.443</v>
       </c>
       <c r="Z679" t="n">
         <v>7297.21</v>
@@ -64491,7 +64491,7 @@
       <c r="W680" t="inlineStr"/>
       <c r="X680" t="inlineStr"/>
       <c r="Y680" t="n">
-        <v>27237.344</v>
+        <v>27252.488</v>
       </c>
       <c r="Z680" t="n">
         <v>32890.07</v>
@@ -64579,7 +64579,7 @@
       <c r="W681" t="inlineStr"/>
       <c r="X681" t="inlineStr"/>
       <c r="Y681" t="n">
-        <v>6976.051</v>
+        <v>6995.246999999999</v>
       </c>
       <c r="Z681" t="n">
         <v>6627.82</v>
@@ -64667,7 +64667,7 @@
       <c r="W682" t="inlineStr"/>
       <c r="X682" t="inlineStr"/>
       <c r="Y682" t="n">
-        <v>6834.126</v>
+        <v>6861.83</v>
       </c>
       <c r="Z682" t="n">
         <v>6517.24</v>
@@ -64755,7 +64755,7 @@
       <c r="W683" t="inlineStr"/>
       <c r="X683" t="inlineStr"/>
       <c r="Y683" t="n">
-        <v>1114.324</v>
+        <v>1142.321</v>
       </c>
       <c r="Z683" t="n">
         <v>815.6700000000001</v>
@@ -64937,7 +64937,7 @@
       <c r="W685" t="inlineStr"/>
       <c r="X685" t="inlineStr"/>
       <c r="Y685" t="n">
-        <v>5393.18</v>
+        <v>5438.876</v>
       </c>
       <c r="Z685" t="n">
         <v>5268.639999999999</v>
@@ -65031,7 +65031,7 @@
       <c r="W686" t="inlineStr"/>
       <c r="X686" t="inlineStr"/>
       <c r="Y686" t="n">
-        <v>2052.669</v>
+        <v>2086.346</v>
       </c>
       <c r="Z686" t="n">
         <v>1985.54</v>
@@ -65124,9 +65124,15 @@
       <c r="V687" t="inlineStr"/>
       <c r="W687" t="inlineStr"/>
       <c r="X687" t="inlineStr"/>
-      <c r="Y687" t="inlineStr"/>
-      <c r="Z687" t="inlineStr"/>
-      <c r="AA687" t="inlineStr"/>
+      <c r="Y687" t="n">
+        <v>1615.201</v>
+      </c>
+      <c r="Z687" t="n">
+        <v>1620.57</v>
+      </c>
+      <c r="AA687" t="n">
+        <v>205.63941</v>
+      </c>
       <c r="AB687" t="inlineStr">
         <is>
           <t>SAMA I MODULO</t>
@@ -65285,7 +65291,7 @@
       <c r="W689" t="inlineStr"/>
       <c r="X689" t="inlineStr"/>
       <c r="Y689" t="n">
-        <v>807.08</v>
+        <v>806.5799999999999</v>
       </c>
       <c r="Z689" t="n">
         <v>766.35</v>
@@ -65373,7 +65379,7 @@
       <c r="W690" t="inlineStr"/>
       <c r="X690" t="inlineStr"/>
       <c r="Y690" t="n">
-        <v>1897.09</v>
+        <v>1947.124</v>
       </c>
       <c r="Z690" t="n">
         <v>1725.3</v>
@@ -65461,7 +65467,7 @@
       <c r="W691" t="inlineStr"/>
       <c r="X691" t="inlineStr"/>
       <c r="Y691" t="n">
-        <v>1087.503</v>
+        <v>1089.242</v>
       </c>
       <c r="Z691" t="n">
         <v>1070.3</v>
@@ -65549,7 +65555,7 @@
       <c r="W692" t="inlineStr"/>
       <c r="X692" t="inlineStr"/>
       <c r="Y692" t="n">
-        <v>434.223</v>
+        <v>433.622</v>
       </c>
       <c r="Z692" t="n">
         <v>160.74</v>
@@ -65637,7 +65643,7 @@
       <c r="W693" t="inlineStr"/>
       <c r="X693" t="inlineStr"/>
       <c r="Y693" t="n">
-        <v>2549.005</v>
+        <v>2610.685</v>
       </c>
       <c r="Z693" t="n">
         <v>2205.58</v>
@@ -65725,7 +65731,7 @@
       <c r="W694" t="inlineStr"/>
       <c r="X694" t="inlineStr"/>
       <c r="Y694" t="n">
-        <v>10151.33</v>
+        <v>11122.467</v>
       </c>
       <c r="Z694" t="n">
         <v>9425.360000000001</v>
@@ -65813,7 +65819,7 @@
       <c r="W695" t="inlineStr"/>
       <c r="X695" t="inlineStr"/>
       <c r="Y695" t="n">
-        <v>3301.075</v>
+        <v>3302.593</v>
       </c>
       <c r="Z695" t="n">
         <v>3184.56</v>
@@ -65907,7 +65913,7 @@
       <c r="W696" t="inlineStr"/>
       <c r="X696" t="inlineStr"/>
       <c r="Y696" t="n">
-        <v>11819.136</v>
+        <v>11493.546</v>
       </c>
       <c r="Z696" t="n">
         <v>11897.51</v>
@@ -66000,15 +66006,9 @@
       <c r="V697" t="inlineStr"/>
       <c r="W697" t="inlineStr"/>
       <c r="X697" t="inlineStr"/>
-      <c r="Y697" t="n">
-        <v>1877.264</v>
-      </c>
-      <c r="Z697" t="n">
-        <v>1775.04</v>
-      </c>
-      <c r="AA697" t="n">
-        <v>232.97544</v>
-      </c>
+      <c r="Y697" t="inlineStr"/>
+      <c r="Z697" t="inlineStr"/>
+      <c r="AA697" t="inlineStr"/>
       <c r="AB697" t="inlineStr">
         <is>
           <t>SAMA I MODULO</t>
@@ -66263,7 +66263,7 @@
       <c r="W700" t="inlineStr"/>
       <c r="X700" t="inlineStr"/>
       <c r="Y700" t="n">
-        <v>31703.216</v>
+        <v>32401.846</v>
       </c>
       <c r="Z700" t="n">
         <v>35878.37</v>
@@ -66349,7 +66349,7 @@
       <c r="W701" t="inlineStr"/>
       <c r="X701" t="inlineStr"/>
       <c r="Y701" t="n">
-        <v>1885.85</v>
+        <v>1883.66</v>
       </c>
       <c r="Z701" t="n">
         <v>2488.43</v>
@@ -66443,7 +66443,7 @@
       <c r="W702" t="inlineStr"/>
       <c r="X702" t="inlineStr"/>
       <c r="Y702" t="n">
-        <v>1342.87</v>
+        <v>1358.02</v>
       </c>
       <c r="Z702" t="n">
         <v>1217.15</v>
@@ -66537,7 +66537,7 @@
       <c r="W703" t="inlineStr"/>
       <c r="X703" t="inlineStr"/>
       <c r="Y703" t="n">
-        <v>1160.555</v>
+        <v>1167.472</v>
       </c>
       <c r="Z703" t="n">
         <v>852.99</v>
@@ -66630,9 +66630,15 @@
       <c r="V704" t="inlineStr"/>
       <c r="W704" t="inlineStr"/>
       <c r="X704" t="inlineStr"/>
-      <c r="Y704" t="inlineStr"/>
-      <c r="Z704" t="inlineStr"/>
-      <c r="AA704" t="inlineStr"/>
+      <c r="Y704" t="n">
+        <v>171.06</v>
+      </c>
+      <c r="Z704" t="n">
+        <v>171.25</v>
+      </c>
+      <c r="AA704" t="n">
+        <v>0</v>
+      </c>
       <c r="AB704" t="inlineStr">
         <is>
           <t>SAMA I MODULO</t>
@@ -66719,7 +66725,7 @@
       <c r="W705" t="inlineStr"/>
       <c r="X705" t="inlineStr"/>
       <c r="Y705" t="n">
-        <v>1820.417</v>
+        <v>1817.962</v>
       </c>
       <c r="Z705" t="n">
         <v>1693.84</v>
@@ -66901,7 +66907,7 @@
       <c r="W707" t="inlineStr"/>
       <c r="X707" t="inlineStr"/>
       <c r="Y707" t="n">
-        <v>2456.163</v>
+        <v>2457.429</v>
       </c>
       <c r="Z707" t="n">
         <v>2420.04</v>
@@ -67555,7 +67561,7 @@
       <c r="W715" t="inlineStr"/>
       <c r="X715" t="inlineStr"/>
       <c r="Y715" t="n">
-        <v>1343.292</v>
+        <v>1357.487</v>
       </c>
       <c r="Z715" t="n">
         <v>1224.3</v>
@@ -67641,13 +67647,13 @@
       <c r="W716" t="inlineStr"/>
       <c r="X716" t="inlineStr"/>
       <c r="Y716" t="n">
-        <v>66138.99400000001</v>
+        <v>66401.215</v>
       </c>
       <c r="Z716" t="n">
-        <v>75426.78999999999</v>
+        <v>75481.63</v>
       </c>
       <c r="AA716" t="n">
-        <v>15566.466</v>
+        <v>15578.512</v>
       </c>
       <c r="AB716" t="inlineStr">
         <is>
@@ -67815,10 +67821,10 @@
       <c r="W718" t="inlineStr"/>
       <c r="X718" t="inlineStr"/>
       <c r="Y718" t="n">
-        <v>341.677</v>
+        <v>1128.857</v>
       </c>
       <c r="Z718" t="n">
-        <v>312.3200000000001</v>
+        <v>312.32</v>
       </c>
       <c r="AA718" t="n">
         <v>33.82722</v>
@@ -67909,7 +67915,7 @@
       <c r="W719" t="inlineStr"/>
       <c r="X719" t="inlineStr"/>
       <c r="Y719" t="n">
-        <v>3915.889</v>
+        <v>3997.481</v>
       </c>
       <c r="Z719" t="n">
         <v>3835.66</v>
@@ -68003,7 +68009,7 @@
       <c r="W720" t="inlineStr"/>
       <c r="X720" t="inlineStr"/>
       <c r="Y720" t="n">
-        <v>218.89</v>
+        <v>218.29</v>
       </c>
       <c r="Z720" t="n">
         <v>168.62</v>
@@ -68099,7 +68105,7 @@
       <c r="W721" t="inlineStr"/>
       <c r="X721" t="inlineStr"/>
       <c r="Y721" t="n">
-        <v>661.372</v>
+        <v>657.862</v>
       </c>
       <c r="Z721" t="n">
         <v>459.29</v>
@@ -68193,13 +68199,13 @@
       <c r="W722" t="inlineStr"/>
       <c r="X722" t="inlineStr"/>
       <c r="Y722" t="n">
-        <v>2928.49</v>
+        <v>2978.008</v>
       </c>
       <c r="Z722" t="n">
         <v>2872.66</v>
       </c>
       <c r="AA722" t="n">
-        <v>551.9669699999999</v>
+        <v>551.9669700000001</v>
       </c>
       <c r="AB722" t="inlineStr">
         <is>
@@ -68287,10 +68293,10 @@
       <c r="W723" t="inlineStr"/>
       <c r="X723" t="inlineStr"/>
       <c r="Y723" t="n">
-        <v>5591.467</v>
+        <v>5707.606</v>
       </c>
       <c r="Z723" t="n">
-        <v>5418.81</v>
+        <v>5418.809999999999</v>
       </c>
       <c r="AA723" t="n">
         <v>979.44147</v>
@@ -68381,7 +68387,7 @@
       <c r="W724" t="inlineStr"/>
       <c r="X724" t="inlineStr"/>
       <c r="Y724" t="n">
-        <v>394.81</v>
+        <v>396.705</v>
       </c>
       <c r="Z724" t="n">
         <v>218.72</v>
@@ -68474,15 +68480,9 @@
       <c r="V725" t="inlineStr"/>
       <c r="W725" t="inlineStr"/>
       <c r="X725" t="inlineStr"/>
-      <c r="Y725" t="n">
-        <v>5695.015</v>
-      </c>
-      <c r="Z725" t="n">
-        <v>5305.05</v>
-      </c>
-      <c r="AA725" t="n">
-        <v>872.3206500000001</v>
-      </c>
+      <c r="Y725" t="inlineStr"/>
+      <c r="Z725" t="inlineStr"/>
+      <c r="AA725" t="inlineStr"/>
       <c r="AB725" t="inlineStr">
         <is>
           <t>SAMA I MODULO</t>
@@ -68563,7 +68563,7 @@
       <c r="W726" t="inlineStr"/>
       <c r="X726" t="inlineStr"/>
       <c r="Y726" t="n">
-        <v>3054.75</v>
+        <v>3064.297</v>
       </c>
       <c r="Z726" t="n">
         <v>2846.68</v>
@@ -68651,7 +68651,7 @@
       <c r="W727" t="inlineStr"/>
       <c r="X727" t="inlineStr"/>
       <c r="Y727" t="n">
-        <v>4580.645</v>
+        <v>4586.177</v>
       </c>
       <c r="Z727" t="n">
         <v>3989.36</v>
@@ -68739,7 +68739,7 @@
       <c r="W728" t="inlineStr"/>
       <c r="X728" t="inlineStr"/>
       <c r="Y728" t="n">
-        <v>1215.474</v>
+        <v>1214.873</v>
       </c>
       <c r="Z728" t="n">
         <v>1095.19</v>
@@ -68827,7 +68827,7 @@
       <c r="W729" t="inlineStr"/>
       <c r="X729" t="inlineStr"/>
       <c r="Y729" t="n">
-        <v>1220.579</v>
+        <v>1220.318</v>
       </c>
       <c r="Z729" t="n">
         <v>1114.26</v>
@@ -68915,7 +68915,7 @@
       <c r="W730" t="inlineStr"/>
       <c r="X730" t="inlineStr"/>
       <c r="Y730" t="n">
-        <v>1327.024</v>
+        <v>1358.674</v>
       </c>
       <c r="Z730" t="n">
         <v>1246.7</v>
@@ -69003,7 +69003,7 @@
       <c r="W731" t="inlineStr"/>
       <c r="X731" t="inlineStr"/>
       <c r="Y731" t="n">
-        <v>1536.549</v>
+        <v>1534.868</v>
       </c>
       <c r="Z731" t="n">
         <v>1482.91</v>
@@ -69091,7 +69091,7 @@
       <c r="W732" t="inlineStr"/>
       <c r="X732" t="inlineStr"/>
       <c r="Y732" t="n">
-        <v>654.627</v>
+        <v>654.684</v>
       </c>
       <c r="Z732" t="n">
         <v>548.05</v>
@@ -69179,7 +69179,7 @@
       <c r="W733" t="inlineStr"/>
       <c r="X733" t="inlineStr"/>
       <c r="Y733" t="n">
-        <v>297.353</v>
+        <v>296.767</v>
       </c>
       <c r="Z733" t="n">
         <v>134.34</v>
@@ -69267,7 +69267,7 @@
       <c r="W734" t="inlineStr"/>
       <c r="X734" t="inlineStr"/>
       <c r="Y734" t="n">
-        <v>640.4690000000001</v>
+        <v>639.287</v>
       </c>
       <c r="Z734" t="n">
         <v>638.78</v>
@@ -69355,7 +69355,7 @@
       <c r="W735" t="inlineStr"/>
       <c r="X735" t="inlineStr"/>
       <c r="Y735" t="n">
-        <v>2136.79</v>
+        <v>2162.13</v>
       </c>
       <c r="Z735" t="n">
         <v>2634</v>
@@ -69443,7 +69443,7 @@
       <c r="W736" t="inlineStr"/>
       <c r="X736" t="inlineStr"/>
       <c r="Y736" t="n">
-        <v>708.904</v>
+        <v>707.742</v>
       </c>
       <c r="Z736" t="n">
         <v>669.77</v>
@@ -69613,10 +69613,10 @@
       <c r="W738" t="inlineStr"/>
       <c r="X738" t="inlineStr"/>
       <c r="Y738" t="n">
-        <v>0</v>
+        <v>5095.09</v>
       </c>
       <c r="Z738" t="n">
-        <v>0</v>
+        <v>340.68</v>
       </c>
       <c r="AA738" t="n">
         <v>0</v>
@@ -69701,7 +69701,7 @@
       <c r="W739" t="inlineStr"/>
       <c r="X739" t="inlineStr"/>
       <c r="Y739" t="n">
-        <v>1891.078</v>
+        <v>1889.876</v>
       </c>
       <c r="Z739" t="n">
         <v>1841.98</v>
@@ -69788,9 +69788,15 @@
       <c r="V740" t="inlineStr"/>
       <c r="W740" t="inlineStr"/>
       <c r="X740" t="inlineStr"/>
-      <c r="Y740" t="inlineStr"/>
-      <c r="Z740" t="inlineStr"/>
-      <c r="AA740" t="inlineStr"/>
+      <c r="Y740" t="n">
+        <v>1786.321</v>
+      </c>
+      <c r="Z740" t="n">
+        <v>1334.13</v>
+      </c>
+      <c r="AA740" t="n">
+        <v>187.8229</v>
+      </c>
       <c r="AB740" t="inlineStr">
         <is>
           <t>SAMA I MODULO</t>
@@ -70117,7 +70123,7 @@
       <c r="W744" t="inlineStr"/>
       <c r="X744" t="inlineStr"/>
       <c r="Y744" t="n">
-        <v>1370.58</v>
+        <v>1374.573</v>
       </c>
       <c r="Z744" t="n">
         <v>1125.48</v>
@@ -70204,15 +70210,9 @@
       <c r="V745" t="inlineStr"/>
       <c r="W745" t="inlineStr"/>
       <c r="X745" t="inlineStr"/>
-      <c r="Y745" t="n">
-        <v>10576.086</v>
-      </c>
-      <c r="Z745" t="n">
-        <v>10462.97</v>
-      </c>
-      <c r="AA745" t="n">
-        <v>2217.440764</v>
-      </c>
+      <c r="Y745" t="inlineStr"/>
+      <c r="Z745" t="inlineStr"/>
+      <c r="AA745" t="inlineStr"/>
       <c r="AB745" t="inlineStr">
         <is>
           <t>SAMA I MODULO</t>
@@ -70292,15 +70292,9 @@
       <c r="V746" t="inlineStr"/>
       <c r="W746" t="inlineStr"/>
       <c r="X746" t="inlineStr"/>
-      <c r="Y746" t="n">
-        <v>7746.997</v>
-      </c>
-      <c r="Z746" t="n">
-        <v>7783.78</v>
-      </c>
-      <c r="AA746" t="n">
-        <v>1088.41867</v>
-      </c>
+      <c r="Y746" t="inlineStr"/>
+      <c r="Z746" t="inlineStr"/>
+      <c r="AA746" t="inlineStr"/>
       <c r="AB746" t="inlineStr">
         <is>
           <t>SAMA I MODULO</t>
@@ -70380,15 +70374,9 @@
       <c r="V747" t="inlineStr"/>
       <c r="W747" t="inlineStr"/>
       <c r="X747" t="inlineStr"/>
-      <c r="Y747" t="n">
-        <v>10619.13</v>
-      </c>
-      <c r="Z747" t="n">
-        <v>9989.57</v>
-      </c>
-      <c r="AA747" t="n">
-        <v>2504.718</v>
-      </c>
+      <c r="Y747" t="inlineStr"/>
+      <c r="Z747" t="inlineStr"/>
+      <c r="AA747" t="inlineStr"/>
       <c r="AB747" t="inlineStr">
         <is>
           <t>SAMA I MODULO</t>
@@ -70468,15 +70456,9 @@
       <c r="V748" t="inlineStr"/>
       <c r="W748" t="inlineStr"/>
       <c r="X748" t="inlineStr"/>
-      <c r="Y748" t="n">
-        <v>8045.398</v>
-      </c>
-      <c r="Z748" t="n">
-        <v>5220.47</v>
-      </c>
-      <c r="AA748" t="n">
-        <v>597.5371</v>
-      </c>
+      <c r="Y748" t="inlineStr"/>
+      <c r="Z748" t="inlineStr"/>
+      <c r="AA748" t="inlineStr"/>
       <c r="AB748" t="inlineStr">
         <is>
           <t>SAMA I MODULO</t>
@@ -70556,9 +70538,15 @@
       <c r="V749" t="inlineStr"/>
       <c r="W749" t="inlineStr"/>
       <c r="X749" t="inlineStr"/>
-      <c r="Y749" t="inlineStr"/>
-      <c r="Z749" t="inlineStr"/>
-      <c r="AA749" t="inlineStr"/>
+      <c r="Y749" t="n">
+        <v>2125.2</v>
+      </c>
+      <c r="Z749" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA749" t="n">
+        <v>0</v>
+      </c>
       <c r="AB749" t="inlineStr">
         <is>
           <t>SAMA I MODULO</t>
@@ -70639,7 +70627,7 @@
       <c r="W750" t="inlineStr"/>
       <c r="X750" t="inlineStr"/>
       <c r="Y750" t="n">
-        <v>4331.305</v>
+        <v>4361.274</v>
       </c>
       <c r="Z750" t="n">
         <v>4125.34</v>
@@ -70727,7 +70715,7 @@
       <c r="W751" t="inlineStr"/>
       <c r="X751" t="inlineStr"/>
       <c r="Y751" t="n">
-        <v>3256.156</v>
+        <v>3254.127</v>
       </c>
       <c r="Z751" t="n">
         <v>3901.82</v>
@@ -70815,13 +70803,13 @@
       <c r="W752" t="inlineStr"/>
       <c r="X752" t="inlineStr"/>
       <c r="Y752" t="n">
-        <v>5208.191</v>
+        <v>5211.146</v>
       </c>
       <c r="Z752" t="n">
         <v>5110.55</v>
       </c>
       <c r="AA752" t="n">
-        <v>847.05164</v>
+        <v>847.0516400000001</v>
       </c>
       <c r="AB752" t="inlineStr">
         <is>
@@ -70903,10 +70891,10 @@
       <c r="W753" t="inlineStr"/>
       <c r="X753" t="inlineStr"/>
       <c r="Y753" t="n">
-        <v>6138.227</v>
+        <v>6136.343</v>
       </c>
       <c r="Z753" t="n">
-        <v>6823.34</v>
+        <v>6783.4</v>
       </c>
       <c r="AA753" t="n">
         <v>317.00065</v>
@@ -70991,7 +70979,7 @@
       <c r="W754" t="inlineStr"/>
       <c r="X754" t="inlineStr"/>
       <c r="Y754" t="n">
-        <v>3059.666</v>
+        <v>3082.98</v>
       </c>
       <c r="Z754" t="n">
         <v>2938.48</v>
@@ -71079,13 +71067,13 @@
       <c r="W755" t="inlineStr"/>
       <c r="X755" t="inlineStr"/>
       <c r="Y755" t="n">
-        <v>6642.24</v>
+        <v>6641.01</v>
       </c>
       <c r="Z755" t="n">
-        <v>2930.04</v>
+        <v>3026.04</v>
       </c>
       <c r="AA755" t="n">
-        <v>122.514</v>
+        <v>140.016</v>
       </c>
       <c r="AB755" t="inlineStr">
         <is>
@@ -71167,7 +71155,7 @@
       <c r="W756" t="inlineStr"/>
       <c r="X756" t="inlineStr"/>
       <c r="Y756" t="n">
-        <v>14034.829</v>
+        <v>13600.254</v>
       </c>
       <c r="Z756" t="n">
         <v>6580.67</v>
@@ -71255,10 +71243,10 @@
       <c r="W757" t="inlineStr"/>
       <c r="X757" t="inlineStr"/>
       <c r="Y757" t="n">
-        <v>3042.857</v>
+        <v>3265.597</v>
       </c>
       <c r="Z757" t="n">
-        <v>2974.36</v>
+        <v>3234.67</v>
       </c>
       <c r="AA757" t="n">
         <v>301.0483</v>
@@ -71343,7 +71331,7 @@
       <c r="W758" t="inlineStr"/>
       <c r="X758" t="inlineStr"/>
       <c r="Y758" t="n">
-        <v>485.098</v>
+        <v>484.526</v>
       </c>
       <c r="Z758" t="n">
         <v>466.34</v>
@@ -71431,7 +71419,7 @@
       <c r="W759" t="inlineStr"/>
       <c r="X759" t="inlineStr"/>
       <c r="Y759" t="n">
-        <v>595.241</v>
+        <v>594.641</v>
       </c>
       <c r="Z759" t="n">
         <v>499.64</v>
@@ -71518,15 +71506,9 @@
       <c r="V760" t="inlineStr"/>
       <c r="W760" t="inlineStr"/>
       <c r="X760" t="inlineStr"/>
-      <c r="Y760" t="n">
-        <v>3921.576</v>
-      </c>
-      <c r="Z760" t="n">
-        <v>3689.3</v>
-      </c>
-      <c r="AA760" t="n">
-        <v>568.5770699999999</v>
-      </c>
+      <c r="Y760" t="inlineStr"/>
+      <c r="Z760" t="inlineStr"/>
+      <c r="AA760" t="inlineStr"/>
       <c r="AB760" t="inlineStr">
         <is>
           <t>SAMA I MODULO</t>
@@ -71607,7 +71589,7 @@
       <c r="W761" t="inlineStr"/>
       <c r="X761" t="inlineStr"/>
       <c r="Y761" t="n">
-        <v>1506.613</v>
+        <v>1505.506</v>
       </c>
       <c r="Z761" t="n">
         <v>772.74</v>
@@ -71694,15 +71676,9 @@
       <c r="V762" t="inlineStr"/>
       <c r="W762" t="inlineStr"/>
       <c r="X762" t="inlineStr"/>
-      <c r="Y762" t="n">
-        <v>1499.937</v>
-      </c>
-      <c r="Z762" t="n">
-        <v>1445.56</v>
-      </c>
-      <c r="AA762" t="n">
-        <v>268.03946</v>
-      </c>
+      <c r="Y762" t="inlineStr"/>
+      <c r="Z762" t="inlineStr"/>
+      <c r="AA762" t="inlineStr"/>
       <c r="AB762" t="inlineStr">
         <is>
           <t>SAMA I MODULO</t>
@@ -71783,7 +71759,7 @@
       <c r="W763" t="inlineStr"/>
       <c r="X763" t="inlineStr"/>
       <c r="Y763" t="n">
-        <v>598.873</v>
+        <v>598.394</v>
       </c>
       <c r="Z763" t="n">
         <v>537.88</v>
@@ -71871,10 +71847,10 @@
       <c r="W764" t="inlineStr"/>
       <c r="X764" t="inlineStr"/>
       <c r="Y764" t="n">
-        <v>1606.887</v>
+        <v>1762.283</v>
       </c>
       <c r="Z764" t="n">
-        <v>1246.08</v>
+        <v>1721.41</v>
       </c>
       <c r="AA764" t="n">
         <v>0</v>
@@ -73187,7 +73163,7 @@
       <c r="W780" t="inlineStr"/>
       <c r="X780" t="inlineStr"/>
       <c r="Y780" t="n">
-        <v>102498.213</v>
+        <v>103698.519</v>
       </c>
       <c r="Z780" t="n">
         <v>143433.03</v>
@@ -73273,7 +73249,7 @@
       <c r="W781" t="inlineStr"/>
       <c r="X781" t="inlineStr"/>
       <c r="Y781" t="n">
-        <v>31249.3</v>
+        <v>31704.389</v>
       </c>
       <c r="Z781" t="n">
         <v>29795.33</v>
@@ -73359,7 +73335,7 @@
       <c r="W782" t="inlineStr"/>
       <c r="X782" t="inlineStr"/>
       <c r="Y782" t="n">
-        <v>17467.784</v>
+        <v>17493.526</v>
       </c>
       <c r="Z782" t="n">
         <v>16611.17</v>
@@ -73445,7 +73421,7 @@
       <c r="W783" t="inlineStr"/>
       <c r="X783" t="inlineStr"/>
       <c r="Y783" t="n">
-        <v>15238.872</v>
+        <v>15331.42</v>
       </c>
       <c r="Z783" t="n">
         <v>14530.26</v>
@@ -73531,7 +73507,7 @@
       <c r="W784" t="inlineStr"/>
       <c r="X784" t="inlineStr"/>
       <c r="Y784" t="n">
-        <v>13151.718</v>
+        <v>13158.493</v>
       </c>
       <c r="Z784" t="n">
         <v>15390.77</v>
@@ -73617,13 +73593,13 @@
       <c r="W785" t="inlineStr"/>
       <c r="X785" t="inlineStr"/>
       <c r="Y785" t="n">
-        <v>15565.46</v>
+        <v>16327.916</v>
       </c>
       <c r="Z785" t="n">
-        <v>13911.7</v>
+        <v>14881.34</v>
       </c>
       <c r="AA785" t="n">
-        <v>3224.07408</v>
+        <v>3287.55711</v>
       </c>
       <c r="AB785" t="inlineStr">
         <is>
@@ -73703,10 +73679,10 @@
       <c r="W786" t="inlineStr"/>
       <c r="X786" t="inlineStr"/>
       <c r="Y786" t="n">
-        <v>10700.635</v>
+        <v>12246.95</v>
       </c>
       <c r="Z786" t="n">
-        <v>11611.16</v>
+        <v>13073.96</v>
       </c>
       <c r="AA786" t="n">
         <v>2685.02112</v>
@@ -73789,10 +73765,10 @@
       <c r="W787" t="inlineStr"/>
       <c r="X787" t="inlineStr"/>
       <c r="Y787" t="n">
-        <v>35133.478</v>
+        <v>35600.292</v>
       </c>
       <c r="Z787" t="n">
-        <v>31165.8</v>
+        <v>31574.43</v>
       </c>
       <c r="AA787" t="n">
         <v>4860.94281</v>
@@ -73875,7 +73851,7 @@
       <c r="W788" t="inlineStr"/>
       <c r="X788" t="inlineStr"/>
       <c r="Y788" t="n">
-        <v>16237.745</v>
+        <v>16253.961</v>
       </c>
       <c r="Z788" t="n">
         <v>15553.08</v>
@@ -73961,7 +73937,7 @@
       <c r="W789" t="inlineStr"/>
       <c r="X789" t="inlineStr"/>
       <c r="Y789" t="n">
-        <v>12322.73</v>
+        <v>12330.935</v>
       </c>
       <c r="Z789" t="n">
         <v>12141.22</v>
@@ -74047,7 +74023,7 @@
       <c r="W790" t="inlineStr"/>
       <c r="X790" t="inlineStr"/>
       <c r="Y790" t="n">
-        <v>16372.083</v>
+        <v>16768.378</v>
       </c>
       <c r="Z790" t="n">
         <v>15887.9</v>
@@ -74219,10 +74195,10 @@
       <c r="W792" t="inlineStr"/>
       <c r="X792" t="inlineStr"/>
       <c r="Y792" t="n">
-        <v>1787.282</v>
+        <v>2464.141</v>
       </c>
       <c r="Z792" t="n">
-        <v>1622.48</v>
+        <v>2303.84</v>
       </c>
       <c r="AA792" t="n">
         <v>254.42478</v>
@@ -74973,7 +74949,7 @@
       <c r="W801" t="inlineStr"/>
       <c r="X801" t="inlineStr"/>
       <c r="Y801" t="n">
-        <v>1343.025</v>
+        <v>1341.883</v>
       </c>
       <c r="Z801" t="n">
         <v>1294.59</v>
@@ -75061,7 +75037,7 @@
       <c r="W802" t="inlineStr"/>
       <c r="X802" t="inlineStr"/>
       <c r="Y802" t="n">
-        <v>3167.881</v>
+        <v>3176.569</v>
       </c>
       <c r="Z802" t="n">
         <v>2681.51</v>
@@ -75155,7 +75131,7 @@
       <c r="W803" t="inlineStr"/>
       <c r="X803" t="inlineStr"/>
       <c r="Y803" t="n">
-        <v>3051.441</v>
+        <v>3055.413</v>
       </c>
       <c r="Z803" t="n">
         <v>2838.01</v>
@@ -75249,7 +75225,7 @@
       <c r="W804" t="inlineStr"/>
       <c r="X804" t="inlineStr"/>
       <c r="Y804" t="n">
-        <v>172.793</v>
+        <v>172.439</v>
       </c>
       <c r="Z804" t="n">
         <v>167.3</v>
@@ -75419,7 +75395,7 @@
       <c r="W806" t="inlineStr"/>
       <c r="X806" t="inlineStr"/>
       <c r="Y806" t="n">
-        <v>1515.795</v>
+        <v>1515.196</v>
       </c>
       <c r="Z806" t="n">
         <v>1587.3</v>
